--- a/online/online.xlsx
+++ b/online/online.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DF499A-9C6C-4643-81B3-4EF4D83C39C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B09B50-FFCA-4740-90D5-A50F4B17D07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="certificate" sheetId="1" r:id="rId1"/>
-    <sheet name="program" sheetId="2" r:id="rId2"/>
+    <sheet name="Link" sheetId="3" r:id="rId1"/>
+    <sheet name="certificate" sheetId="1" r:id="rId2"/>
+    <sheet name="program" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>course name</t>
   </si>
@@ -98,6 +99,15 @@
   </si>
   <si>
     <t>1-Introduction to Computer Science and Programming Using Python    2-Introduction to Computational Thinking and Data Science</t>
+  </si>
+  <si>
+    <t>https://www.edx.org/school/mitx</t>
+  </si>
+  <si>
+    <t>https://www.edx.org/school/harvardx#programs</t>
+  </si>
+  <si>
+    <t>harvard</t>
   </si>
 </sst>
 </file>
@@ -450,6 +460,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FE0ECD-1D8F-4B89-B78A-D0D4EDA3887F}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -584,7 +623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D72185-9694-4517-9016-DDB873E7BE62}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
